--- a/SQExcel.Portal/src/content/docs/ja/docs/images/data-export-dialog/data-export-dialog.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/data-export-dialog/data-export-dialog.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\data-export-dialog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\data-export-dialog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CF767E1-93C6-41C9-BD5F-3D1482DA64C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D324AD7B-A103-4BD3-9000-D4F1C6F34366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="950" yWindow="350" windowWidth="19780" windowHeight="14040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1810" yWindow="1710" windowWidth="23790" windowHeight="14290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data-export-dialog" sheetId="3" r:id="rId1"/>
-    <sheet name="OPERATION_FLOW" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="OPERATION_FLOW" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1290,581 +1292,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>209177</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>22411</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>160469</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>99494</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="13" name="グループ化 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E481E710-93BE-6E4A-6A93-57B27A60EAD1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="209177" y="717176"/>
-          <a:ext cx="8520057" cy="4708847"/>
-          <a:chOff x="209177" y="708211"/>
-          <a:chExt cx="8644442" cy="4649083"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="6" name="グループ化 5">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{491D16D3-0B2D-7371-61C3-F1C5CF28BC7D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="209177" y="708211"/>
-            <a:ext cx="8644442" cy="4649083"/>
-            <a:chOff x="234950" y="1143000"/>
-            <a:chExt cx="8641080" cy="4649082"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="2" name="図 1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DA825BF-54F7-CAFB-E386-CB66F7C5A538}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr>
-              <a:picLocks noChangeAspect="1"/>
-            </xdr:cNvPicPr>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="234950" y="1143000"/>
-              <a:ext cx="8641080" cy="4649082"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="正方形/長方形 2">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7460997-BF7B-4A23-B48C-2A01D96B6963}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="294714" y="1757083"/>
-              <a:ext cx="8495553" cy="1386541"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="正方形/長方形 3">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9EB1E26-29A0-4FBD-A8A2-D3B9D37DD8D4}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="302186" y="3245224"/>
-              <a:ext cx="8495553" cy="775447"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="正方形/長方形 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{248A3D22-243C-4720-B7F3-7C4C7E1AF76A}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="309656" y="4144681"/>
-              <a:ext cx="8495553" cy="1195296"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="19050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="2">
-              <a:schemeClr val="accent1">
-                <a:shade val="15000"/>
-              </a:schemeClr>
-            </a:lnRef>
-            <a:fillRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="lt1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-              <a:prstTxWarp prst="textNoShape">
-                <a:avLst/>
-              </a:prstTxWarp>
-              <a:noAutofit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="7" name="四角形: 角を丸くする 6">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{694FE05B-E18F-4076-AF61-948297ED5514}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8167221" y="1903505"/>
-            <a:ext cx="470918" cy="266265"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>①</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="8" name="四角形: 角を丸くする 7">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F0F13B2-1105-4BEB-B37D-31EED9883C6F}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8167221" y="3200400"/>
-            <a:ext cx="470919" cy="266264"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>②</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="9" name="四角形: 角を丸くする 8">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A86E64B0-2CCB-4C9D-8823-178D7185D924}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="8167221" y="4226858"/>
-            <a:ext cx="478015" cy="266265"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>③</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="11" name="四角形: 角を丸くする 10">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{608F460B-0352-DAD5-0CD3-EA3E69C04F92}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3804771" y="3838762"/>
-            <a:ext cx="582333" cy="243542"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>③</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>-1</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="四角形: 角を丸くする 11">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D94517E-3AD6-F470-049E-176EC10B564A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3805637" y="4166525"/>
-            <a:ext cx="582333" cy="243542"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>③</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>-2</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>108882</xdr:colOff>
       <xdr:row>17</xdr:row>
@@ -1954,224 +1381,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>7470</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>224119</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>190350</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>66270</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="19" name="グループ化 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B03A923-D7DF-3A1A-760F-5C2A10B4D640}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="239058" y="6477001"/>
-          <a:ext cx="8520057" cy="1231681"/>
-          <a:chOff x="242420" y="6396319"/>
-          <a:chExt cx="8641080" cy="1213751"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="14" name="図 13">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42C70E97-AC3C-5D78-F4C5-25DC4D1707FE}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="242420" y="6396319"/>
-            <a:ext cx="8641080" cy="1213751"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="15" name="四角形: 角を丸くする 14">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8354922D-7D97-4112-8A87-D414094F0940}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7121072" y="6482443"/>
-            <a:ext cx="586094" cy="243172"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>③</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>-4</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="四角形: 角を丸くする 17">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C424A04-D70A-4475-8B4E-B54957569119}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7346950" y="7023100"/>
-            <a:ext cx="586094" cy="243172"/>
-          </a:xfrm>
-          <a:prstGeom prst="roundRect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>③</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>-5</a:t>
-            </a:r>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>89649</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>46</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>218704</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -2187,7 +1404,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="10047943"/>
+          <a:off x="231588" y="13521767"/>
           <a:ext cx="10650071" cy="4992408"/>
           <a:chOff x="234950" y="8547849"/>
           <a:chExt cx="10801350" cy="4929655"/>
@@ -2207,7 +1424,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2282,244 +1499,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>216647</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>29882</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>167939</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>832</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="30" name="グループ化 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB89F09D-BBFE-0514-762E-621E05AFD8B6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="216647" y="16241058"/>
-          <a:ext cx="8520057" cy="4834303"/>
-          <a:chOff x="216647" y="15574682"/>
-          <a:chExt cx="8644442" cy="4771550"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="21" name="図 20">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4CB2EE9-C0E2-3751-CDD3-8C392AEADECB}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="216647" y="15574682"/>
-            <a:ext cx="8644442" cy="4771550"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="26" name="正方形/長方形 25">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D225630-7DB3-4374-B266-40F39ED470F2}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="391832" y="19483294"/>
-            <a:ext cx="3449544" cy="288366"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="28" name="正方形/長方形 27">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB04F7DE-83B4-41C2-9286-2EDEFDC647FB}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="384361" y="17972741"/>
-            <a:ext cx="6578600" cy="487082"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="29" name="正方形/長方形 28">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{499CD94F-B319-4B61-8B23-8204A8168D06}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5120715" y="19262165"/>
-            <a:ext cx="2405155" cy="288364"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>7471</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>44823</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
       <xdr:colOff>4483</xdr:colOff>
-      <xdr:row>150</xdr:row>
+      <xdr:row>165</xdr:row>
       <xdr:rowOff>220620</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -2535,7 +1523,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="239059" y="28993352"/>
+          <a:off x="239059" y="32467176"/>
           <a:ext cx="10650071" cy="5965503"/>
           <a:chOff x="201706" y="28391223"/>
           <a:chExt cx="10804712" cy="5890797"/>
@@ -2555,7 +1543,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2632,13 +1620,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>29883</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>46</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>119</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>191665</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -2654,7 +1642,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="22030765"/>
+          <a:off x="231588" y="25504589"/>
           <a:ext cx="10650071" cy="5719900"/>
           <a:chOff x="234950" y="21746883"/>
           <a:chExt cx="10801350" cy="5648182"/>
@@ -2693,7 +1681,7 @@
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
           <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
@@ -2822,10 +1810,1589 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>209177</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>160469</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>99494</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DA825BF-54F7-CAFB-E386-CB66F7C5A538}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="209177" y="717176"/>
+          <a:ext cx="8520057" cy="4708847"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>36516</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>181212</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>75907</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>196047</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7460997-BF7B-4A23-B48C-2A01D96B6963}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="268104" y="1339153"/>
+          <a:ext cx="8376568" cy="1404365"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>43883</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>67366</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>83274</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>158017</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9EB1E26-29A0-4FBD-A8A2-D3B9D37DD8D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="275471" y="2846425"/>
+          <a:ext cx="8376568" cy="785416"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>51249</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>52032</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>90640</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>104753</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{248A3D22-243C-4720-B7F3-7C4C7E1AF76A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="282837" y="3757444"/>
+          <a:ext cx="8376568" cy="1210662"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>178713</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>75130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>179679</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>113230</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="四角形: 角を丸くする 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{694FE05B-E18F-4076-AF61-948297ED5514}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8052713" y="1927836"/>
+          <a:ext cx="464142" cy="269688"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>①</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>178713</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>230755</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>179680</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>37265</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="四角形: 角を丸くする 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F0F13B2-1105-4BEB-B37D-31EED9883C6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8052713" y="3241402"/>
+          <a:ext cx="464143" cy="269687"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>②</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>178713</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>112467</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>186674</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>150567</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="四角形: 角を丸くする 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A86E64B0-2CCB-4C9D-8823-178D7185D924}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8052713" y="4281055"/>
+          <a:ext cx="471137" cy="269688"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>③</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>47622</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>182558</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>158400</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>197643</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="四角形: 角を丸くする 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{608F460B-0352-DAD5-0CD3-EA3E69C04F92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3753034" y="3887970"/>
+          <a:ext cx="573954" cy="246673"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>③</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>-1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>48475</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>51359</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>159253</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66444</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="四角形: 角を丸くする 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D94517E-3AD6-F470-049E-176EC10B564A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3753887" y="4219947"/>
+          <a:ext cx="573954" cy="246673"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>③</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>-2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>39807</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>82944</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>54514</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>64285</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="図 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EFE9CF2-5B30-9B8A-FA4E-A4E20441EE5B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="271395" y="777709"/>
+          <a:ext cx="246295" cy="212929"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>216647</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>29882</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>167939</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>832</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="47" name="グループ化 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09A79FA2-CAAA-B083-12A2-DB78431A48A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="216647" y="19714882"/>
+          <a:ext cx="8520057" cy="4834303"/>
+          <a:chOff x="216647" y="19460882"/>
+          <a:chExt cx="8644442" cy="4771550"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="30" name="グループ化 29">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB89F09D-BBFE-0514-762E-621E05AFD8B6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="216647" y="19460882"/>
+            <a:ext cx="8644442" cy="4771550"/>
+            <a:chOff x="216647" y="15574682"/>
+            <a:chExt cx="8644442" cy="4771550"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="図 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4CB2EE9-C0E2-3751-CDD3-8C392AEADECB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="216647" y="15574682"/>
+              <a:ext cx="8644442" cy="4771550"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="26" name="正方形/長方形 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D225630-7DB3-4374-B266-40F39ED470F2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="391832" y="19483294"/>
+              <a:ext cx="3449544" cy="288366"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="28" name="正方形/長方形 27">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB04F7DE-83B4-41C2-9286-2EDEFDC647FB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="384361" y="17972741"/>
+              <a:ext cx="6578600" cy="487082"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="29" name="正方形/長方形 28">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{499CD94F-B319-4B61-8B23-8204A8168D06}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5120715" y="19262165"/>
+              <a:ext cx="2405155" cy="288364"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="46" name="図 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7347C41-DC8B-BEC4-0F4A-C5280D99D975}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="287867" y="19524693"/>
+            <a:ext cx="250825" cy="229986"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>77083</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="19" name="グループ化 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C87227D-2197-42E4-DC7F-16C624235649}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="231588" y="6484471"/>
+          <a:ext cx="8520057" cy="4708847"/>
+          <a:chOff x="234950" y="6400800"/>
+          <a:chExt cx="8641080" cy="4649083"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="45" name="グループ化 44">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB7A319C-1834-E935-590E-8B96FA8AFCAF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="234950" y="6400800"/>
+            <a:ext cx="8641080" cy="4649083"/>
+            <a:chOff x="234950" y="6400800"/>
+            <a:chExt cx="8641080" cy="4649083"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="38" name="グループ化 37">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9CE68D2-BF18-B95C-1CCF-637CDCBD3634}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="234950" y="6400800"/>
+              <a:ext cx="8641080" cy="4649083"/>
+              <a:chOff x="234950" y="6400800"/>
+              <a:chExt cx="8641080" cy="4649083"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="16" name="図 15">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB27C290-5201-AE79-1DDB-CCC7E9B9A7E3}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="234950" y="6400800"/>
+                <a:ext cx="8641080" cy="4649083"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="37" name="図 36">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44CACD4B-47C9-D8C1-368B-C4813CA0E4EC}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="323581" y="7007405"/>
+                <a:ext cx="8479251" cy="872869"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+        </xdr:grpSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="41" name="四角形: 角を丸くする 40">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F019D221-5D2F-4972-828B-A3AC8CBFA4D2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7078382" y="9218706"/>
+              <a:ext cx="584608" cy="243775"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>③</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>-4</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="42" name="四角形: 角を丸くする 41">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18E9B27F-378B-4333-98F1-7920E7EE4263}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7304458" y="9761373"/>
+              <a:ext cx="584608" cy="243776"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>③</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>-5</a:t>
+              </a:r>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:endParaRPr>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="43" name="正方形/長方形 42">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{688E39A9-BB6B-4D5C-AC84-EAFC8C5C9178}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="332068" y="8202706"/>
+              <a:ext cx="8465670" cy="773463"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="44" name="四角形: 角を丸くする 43">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{154F3DF3-FD4F-4C89-B35B-F1980E9B6540}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8010712" y="8637494"/>
+              <a:ext cx="470867" cy="266699"/>
+            </a:xfrm>
+            <a:prstGeom prst="roundRect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFF00"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>②</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="15" name="正方形/長方形 14">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B27E6D4A-B4A2-479A-A341-3B00F4D27C3F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="309656" y="6955118"/>
+            <a:ext cx="8497591" cy="1180247"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="18" name="四角形: 角を丸くする 17">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF0A8A7E-7029-4A05-870D-D5A5F0ED3E76}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8205203" y="7328647"/>
+            <a:ext cx="470866" cy="266700"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>①</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>595257</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>136847</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC6039C2-9F9B-B03F-2F5E-CFAB49C078DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8520057" cy="4708847"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>62218</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>60533</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>308513</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>44862</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE37FE18-0570-2BE5-6F6E-8DED7E382821}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="62218" y="60533"/>
+          <a:ext cx="246295" cy="212929"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -9746,7 +10313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247D8D20-CE8B-4D82-A6C6-EA8B8BD03E4C}">
-  <dimension ref="A2:B584"/>
+  <dimension ref="A2:B599"/>
   <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="16384" width="3.08203125" style="1"/>
@@ -9778,208 +10345,217 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="2"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="1" t="s">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="2"/>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="2"/>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="2"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="1" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="1" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="1" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="1" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="1" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="1" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="1" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="2"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="1" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="2"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B82" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="1" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="1" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="1" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="2"/>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B90" s="2"/>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="1" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="2"/>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B105" s="2"/>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B108" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B94" s="1" t="s">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B109" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B95" s="1" t="s">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B110" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B103" s="2"/>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B117" s="2"/>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122" s="1" t="s">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B118" s="2"/>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B132" s="2"/>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A137" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B137" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B123" s="1" t="s">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B138" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B124" s="1" t="s">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B139" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B125" s="1" t="s">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B140" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="141" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B141" s="2"/>
     </row>
     <row r="156" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B156" s="2"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B175" s="2"/>
-    </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B179" s="2"/>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B171" s="2"/>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B190" s="2"/>
     </row>
     <row r="194" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B194" s="2"/>
     </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B214" s="2"/>
-    </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B233" s="2"/>
-    </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B247" s="2"/>
-    </row>
-    <row r="260" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B260" s="2"/>
-    </row>
-    <row r="269" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B269" s="2"/>
-    </row>
-    <row r="288" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B288" s="2"/>
-    </row>
-    <row r="300" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B300" s="2"/>
-    </row>
-    <row r="312" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B312" s="2"/>
-    </row>
-    <row r="341" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B341" s="2"/>
-    </row>
-    <row r="344" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B344" s="3"/>
-    </row>
-    <row r="367" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B367" s="2"/>
-    </row>
-    <row r="376" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B376" s="2"/>
-    </row>
-    <row r="394" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B394" s="2"/>
-    </row>
-    <row r="395" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B395" s="2"/>
-    </row>
-    <row r="421" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B421" s="2"/>
-    </row>
-    <row r="430" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B430" s="2"/>
-    </row>
-    <row r="447" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B447" s="2"/>
-    </row>
-    <row r="480" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B480" s="2"/>
-    </row>
-    <row r="522" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B522" s="2"/>
-    </row>
-    <row r="549" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B549" s="2"/>
-    </row>
-    <row r="584" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B584" s="2"/>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B209" s="2"/>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B229" s="2"/>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B248" s="2"/>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B262" s="2"/>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B275" s="2"/>
+    </row>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B284" s="2"/>
+    </row>
+    <row r="303" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B303" s="2"/>
+    </row>
+    <row r="315" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B315" s="2"/>
+    </row>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B327" s="2"/>
+    </row>
+    <row r="356" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B356" s="2"/>
+    </row>
+    <row r="359" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B359" s="3"/>
+    </row>
+    <row r="382" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B382" s="2"/>
+    </row>
+    <row r="391" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B391" s="2"/>
+    </row>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B409" s="2"/>
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B410" s="2"/>
+    </row>
+    <row r="436" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B436" s="2"/>
+    </row>
+    <row r="445" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B445" s="2"/>
+    </row>
+    <row r="462" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B462" s="2"/>
+    </row>
+    <row r="495" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B495" s="2"/>
+    </row>
+    <row r="537" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B537" s="2"/>
+    </row>
+    <row r="564" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B564" s="2"/>
+    </row>
+    <row r="599" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B599" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -9990,6 +10566,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84459765-3659-4726-B786-D9AEF4C212A0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29FA320-DA47-41A9-9EA7-7E68689E0E1F}">
   <dimension ref="A1:ED573"/>
   <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
